--- a/event_registration_forms/033_stallholder_operations_form--event_registration_forms.xlsx
+++ b/event_registration_forms/033_stallholder_operations_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>event_title</t>
+          <t>event_details</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>event_title</t>
+          <t>Event Details</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>event_start_date</t>
+          <t>stallholder_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>event_start_date</t>
+          <t>Stallholder Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>event_end_date</t>
+          <t>contact_details</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>event_end_date</t>
+          <t>Contact Details</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>event_location</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>event_location</t>
+          <t>Event ID</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>event_location</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>Event Location</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>event_notes</t>
+          <t>event_status</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>event_notes</t>
+          <t>Event Status</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>stallholder_name</t>
+          <t>Stallholder Name</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>stallholder_status</t>
+          <t>Stallholder Status</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>stallholder_notes</t>
+          <t>Stallholder Notes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_name</t>
+          <t>Contact Name</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>phone_numbers</t>
+          <t>Phone Numbers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>event_id_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>Event Id 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>stallholder_id</t>
+          <t>event_status_id</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>stallholder_id</t>
+          <t>Event Status ID</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>event_status_id</t>
+          <t>event_start_date_id</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>event_status_id</t>
+          <t>Event Start Date ID</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>event_start_date_id</t>
+          <t>event_end_date_id</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>event_start_date_id</t>
+          <t>Event End Date ID</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>event_end_date_id</t>
+          <t>event_start_date</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>event_end_date_id</t>
+          <t>Event Start Date</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>event_location</t>
+          <t>event_end_date</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>event_location</t>
+          <t>Event End Date</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>event_status</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>event_status</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>stallholder_name</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>stallholder_name</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>stallholder_status</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>stallholder_status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>stallholder_notes</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>stallholder_notes</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>contact_name</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>contact_name</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>phone_numbers</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>phone_numbers</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,34 +965,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>event_status_choices</t>
+          <t>event_id_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active',_'label':_'active'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'active', 'label': 'active'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>event_status_choices</t>
+          <t>event_id_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive',_'label':_'inactive'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'inactive', 'label': 'inactive'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1165,46 +1004,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'canceled',_'label':_'canceled'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'canceled', 'label': 'canceled'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>stallholder_status_choices</t>
+          <t>event_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active',_'label':_'active'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'active', 'label': 'active'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>stallholder_status_choices</t>
+          <t>event_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive',_'label':_'inactive'}</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'inactive', 'label': 'inactive'}</t>
+          <t>Canceled</t>
         </is>
       </c>
     </row>
@@ -1216,80 +1055,80 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pending',_'label':_'pending'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'pending', 'label': 'pending'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>event_id_choices</t>
+          <t>stallholder_status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1,_'label':_1}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1, 'label': 1}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>event_id_choices</t>
+          <t>stallholder_status_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2,_'label':_2}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2, 'label': 2}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>stallholder_id_choices</t>
+          <t>event_id_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>stallholder_id_choices</t>
+          <t>event_id_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1386,114 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2, 'label': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>event_status_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'active',_'label':_'active'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'active', 'label': 'active'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>event_status_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'inactive',_'label':_'inactive'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'inactive', 'label': 'inactive'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>event_status_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'canceled',_'label':_'canceled'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'canceled', 'label': 'canceled'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>stallholder_status_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'active',_'label':_'active'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'active', 'label': 'active'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>stallholder_status_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'inactive',_'label':_'inactive'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'inactive', 'label': 'inactive'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>stallholder_status_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'pending',_'label':_'pending'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'pending', 'label': 'pending'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
